--- a/ValueSet-vital-sign-codes-vs.xlsx
+++ b/ValueSet-vital-sign-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T10:04:33+00:00</t>
+    <t>2026-02-09T10:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vital-sign-codes-vs.xlsx
+++ b/ValueSet-vital-sign-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T10:35:12+00:00</t>
+    <t>2026-10-27T13:25:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vital-sign-codes-vs.xlsx
+++ b/ValueSet-vital-sign-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:25:43+00:00</t>
+    <t>2026-10-27T13:28:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
